--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.92083</v>
+        <v>17.24145</v>
       </c>
       <c r="D2" t="n">
-        <v>17.14738</v>
+        <v>16.59804</v>
       </c>
       <c r="E2" t="n">
-        <v>17.51405</v>
+        <v>16.61581</v>
       </c>
       <c r="F2" t="n">
-        <v>44.07202</v>
+        <v>42.47542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0517</v>
+        <v>0.0507</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85292</v>
+        <v>1.86253</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.96864</v>
+        <v>16.94217</v>
       </c>
       <c r="D3" t="n">
-        <v>17.00788</v>
+        <v>16.77569</v>
       </c>
       <c r="E3" t="n">
-        <v>17.21</v>
+        <v>16.90373</v>
       </c>
       <c r="F3" t="n">
-        <v>43.06793</v>
+        <v>43.38314</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05169</v>
+        <v>0.05142</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86657</v>
+        <v>1.84062</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.93293</v>
+        <v>17.13757</v>
       </c>
       <c r="D4" t="n">
-        <v>17.03895</v>
+        <v>16.73589</v>
       </c>
       <c r="E4" t="n">
-        <v>17.12754</v>
+        <v>16.82084</v>
       </c>
       <c r="F4" t="n">
-        <v>44.36633</v>
+        <v>43.62335</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0509</v>
+        <v>0.05196</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85388</v>
+        <v>1.84812</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.15034</v>
+        <v>16.89016</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06134</v>
+        <v>16.309</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63193</v>
+        <v>16.666</v>
       </c>
       <c r="F6" t="n">
-        <v>22.23037</v>
+        <v>22.49089</v>
       </c>
       <c r="G6" t="n">
-        <v>34.99003</v>
+        <v>34.44181</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.13306</v>
+        <v>17.27816</v>
       </c>
       <c r="D7" t="n">
-        <v>16.39264</v>
+        <v>16.53545</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30012</v>
+        <v>16.80427</v>
       </c>
       <c r="F7" t="n">
-        <v>22.04992</v>
+        <v>22.58805</v>
       </c>
       <c r="G7" t="n">
-        <v>34.8783</v>
+        <v>35.18146</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.59062</v>
+        <v>16.99872</v>
       </c>
       <c r="D8" t="n">
-        <v>15.96679</v>
+        <v>16.57655</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59909</v>
+        <v>16.73356</v>
       </c>
       <c r="F8" t="n">
-        <v>22.25021</v>
+        <v>22.30705</v>
       </c>
       <c r="G8" t="n">
-        <v>34.68909</v>
+        <v>34.76035</v>
       </c>
     </row>
   </sheetData>
